--- a/khurana_cv/data/skills.xlsx
+++ b/khurana_cv/data/skills.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\havis\University of Oregon Dropbox\Havi Khurana\Personal\Coding projects\khurana_cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A201150-9CD0-4236-BCD0-7F9FE418DA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73202C3B-CE02-408A-81A0-2649F6C5DF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2200" yWindow="2200" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,13 +42,6 @@
     <t>seq</t>
   </si>
   <si>
-    <t>Worked with cross-sectional, cross-sectional with repeated time longitudinal, and text
-data; Data wrangling, visualization, and preparation for analyses</t>
-  </si>
-  <si>
-    <t>English (Proficient), Hindi (Proficient)</t>
-  </si>
-  <si>
     <t>Statistics and Probability Theory; Generalized Regression Models; Causal Inference/Quasi-Experiment Designs; Program Evaluation; Measurement Theory and Rasch Models; Multivariate Statistics; Monte-Carlo Simulations</t>
   </si>
   <si>
@@ -64,7 +57,14 @@
     <t>Languages</t>
   </si>
   <si>
-    <t>R (Expert); Python (Intermediate); LaTeX (Beginner)</t>
+    <t>Hindi (Proficient), English (Proficient)</t>
+  </si>
+  <si>
+    <t>R (Expert); Stata(Intermediate); Python (Intermediate); LaTeX (Intermediate)</t>
+  </si>
+  <si>
+    <t>Worked with cross-sectional, cross-sectional with repeated time, longitudinal, and text
+data; Data wrangling, visualization, and preparation for analyses; Data analyses and Statistical Modeling</t>
   </si>
 </sst>
 </file>
@@ -424,10 +424,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -438,24 +438,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -466,10 +466,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
